--- a/planning/WIP_Tracker_App_Development_Plan.xlsx
+++ b/planning/WIP_Tracker_App_Development_Plan.xlsx
@@ -20,8 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="10">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd mmm yyyy"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +43,12 @@
       <i val="1"/>
       <color rgb="004B5563"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="009CA3AF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -113,25 +122,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -341,8 +357,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RolesTable" displayName="RolesTable" ref="A4:E10" headerRowCount="1">
-  <autoFilter ref="A4:E10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RolesTable" displayName="RolesTable" ref="A4:E9" headerRowCount="1">
+  <autoFilter ref="A4:E9"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Role Name"/>
     <tableColumn id="2" name="Description"/>
@@ -355,8 +371,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L31" headerRowCount="1">
-  <autoFilter ref="A4:L31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PermissionLevelsTable" displayName="PermissionLevelsTable" ref="A14:E15" headerRowCount="1">
+  <autoFilter ref="A14:E15"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Permission"/>
+    <tableColumn id="2" name="Description"/>
+    <tableColumn id="3" name="Grants"/>
+    <tableColumn id="4" name="Status"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L35" headerRowCount="1">
+  <autoFilter ref="A4:L35"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Feature / Idea"/>
@@ -664,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B31"/>
+  <dimension ref="B2:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -685,162 +715,183 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Last updated: 28 Aug 2026</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>How this workbook is organized</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>•  Roles — define/refine who the app's users are and roughly what they should see. Not finalized yet; add rows and edit freely.</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>•  Roles — define/refine who the app's users fundamentally are and roughly what they should see, plus a separate Permission Levels table for capabilities that get granted on top of a role rather than defining one (see below). Not finalized yet; add rows and edit freely.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>•  Features &amp; Backlog — the master list: everything built already (Status = Done) plus every idea, in priority order. This is the sheet you'll edit most.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>•  Summary — auto-counting dashboard (by Status / Priority) so it's obvious what's outstanding at a glance. Updates itself as you edit the backlog.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Roles vs. Permission Levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>A Role is what someone fundamentally is day to day, and drives their default dashboard (e.g. Job Coordinator, Team Leader). A Permission Level is a capability granted to specific people on top of whichever role(s) they hold, deliberately, rather than something a whole role gets by default — Admin is the first one of these (added, edited and org-charted employees; nobody's entire job is running this tool, so it's a flag applied to whoever needs it, not a standalone role). Treat any future request like "only X should be able to Y" as a candidate for this table rather than a new role, unless it really does describe someone's whole job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>How to use it</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>•  Add a new idea: go to Features &amp; Backlog, add a row at the bottom with the next ID (e.g. F028), fill in what you can — Status "Idea" and Priority are the two that matter most.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>•  Priority, Status, Type and Area are dropdowns (click the cell, use the arrow). Add more Area options on the Lists sheet if a new one doesn't fit.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>•  Visible To (Roles) is free text for now (e.g. "Job Coordinator, Manager") — once the Roles sheet is settled this can become a dropdown too, just say the word.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>•  When you're ready for another round of work, send the file back — I'll read Status = Idea / Planned rows (Priority order), implement, then flip them to Done and fill in Date Shipped / Notes.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Priority levels</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>•  P0 — Critical: broken/blocking, or a hard prerequisite for going live (e.g. auth before real data).</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>•  P1 — High: next up, clearly valuable, no major open questions.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>•  P2 — Medium: worth doing, not urgent.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>•  P3 — Low: nice-to-have, fine to sit in the backlog a while.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Status values</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>•  Idea — captured, not yet scoped or committed to.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>•  Backlog — scoped and agreed, just not started.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+    <row r="28" ht="28" customHeight="1">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>•  Planned — next up / actively being scoped for the next round.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>•  In Progress — actively being built.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>•  Done — shipped, live in the tool.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="B28" s="4" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>•  Won't Do — considered and deliberately dropped (keep it, don't delete — the "why not" is worth keeping).</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>A note on what's pre-filled</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Everything currently marked Done reflects what exists in the standalone demo prototype (demo/wip-tracker-demo.html in the repo) as of this plan's creation — it hasn't been rebuilt against the real server/client yet. "Date Added" is left blank on these since they predate this plan; fill it in going forward for new items. The Idea/Backlog rows below the Done ones are carried over from the original README's "suggested next features" plus things flagged mid-build, so you have a starting point rather than a blank page — re-prioritize, reword or delete freely.</t>
         </is>
@@ -857,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -868,220 +919,266 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Roles</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Draft, based on the roles the demo prototype already assumes. Not finalized — add, rename, split or merge as the real plan takes shape.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Role Name</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Typically Sees / Can Do (draft)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Workshop / Trade Staff</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Anyone doing hands-on task work (welding, fabrication, robotics, etc.)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>My Dashboard only — their own open tasks, slider to update %.</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Deliberately minimal — the guiding principle is staff shouldn't have to navigate to report status.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Team Leader / Production Owner</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Leads a workshop or trade team (e.g. Welding Workshop, Robotics); owns jobs once they reach Production.</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>My Dashboard, Team (own crew + pool capacity), job task-line assignment, Robotics approval queue where relevant.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Can delegate their coverage to someone else when on leave (see Delegation feature).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Job Coordinator</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Owns a job start to finish through the early/late stages; the main point of contact on a job.</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Job Board (move stages, manage holds, triage BC imports), job detail, BC import.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Overlaps with Production Owner on some jobs — same job can have both roles depending on stage.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Manages a group of Team Leaders / Coordinators.</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Everything their reports see, plus Team rollup across reports, WIP Meeting, Analytics.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Scoped via a manager relationship so a manager only ever sees their own reports.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Baseline access every signed-in user gets, regardless of role.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>My Dashboard, All Actions/Register, Getting Started guide.</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Think of specific roles as additive on top of this baseline, not replacing it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Permission Levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Additive capabilities granted to specific people regardless of role — not a standalone role, since nobody's whole job here is running the tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Permission</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Runs the tool itself — user/employee records, configuration.</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Employees directory, and (not yet built) any future settings/config screens.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Applied to whoever needs it (on top of their normal role), not a standalone role — this company has nobody whose whole job is running this tool.</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Add/edit employees, arrange the org chart, manage role definitions.</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Not heavily exercised in the demo yet — flesh out once real config/user-management needs are known.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Everyone</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Baseline access every signed-in user gets, regardless of role.</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>My Dashboard, All Actions/Register, Getting Started guide.</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Think of specific roles as additive on top of this baseline, not replacing it.</t>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Raised directly by Ashley — model as a permission overlay, the same way Robotics approval and delegation already work in the demo, not as entry #6 in the Roles table above.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D5:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Draft,Confirmed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D15:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Confirmed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1296,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1314,1476 +1411,1676 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Features &amp; Backlog</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Sorted Done first (build history), then Idea/Backlog in rough priority order. Sort/filter freely — it's an Excel Table.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Feature / Idea</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Visible To (Roles)</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Requested By</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Date Added</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Date Shipped</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>F001</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Action register</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Company-wide action list (Safety, Quality, Production, Maintenance, Environmental, Training, Other) alongside production jobs, in one register.</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Action Register</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Everyone</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>F002</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Job stage Kanban board</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Drag-and-drop board across the full stage lifecycle: Order Received → Engineering → Procurement → Materials Available → Production → NDT/Testing → Documentation → Ready for Dispatch → Complete. Movable either direction (rework goes backward).</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Job Board</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Job Coordinator, Manager</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>F003</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Task-line model in Production</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Break a job into task lines once it reaches Production: individual staff assignment, Welding Workshop headcount pools, Robotics staff+equipment with a team-leader approval/sign-off workflow.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Job Board</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Team Leader / Production Owner</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>F004</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>My Dashboard</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>"My Actions" (everything assigned to me, completion slider right on the card) plus "Coming To You Next" (jobs where the current task is someone else's but the next one is mine, with expected handover date and risk badge).</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>My Dashboard</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Everyone</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>F005</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Team / Manager view</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>One row per direct report or pool, open/overdue/at-risk counts, expandable task list, workshop pool capacity status.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Team / Manager View</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Team Leader / Production Owner, Manager</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>F006</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>WIP Meeting view</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Every active job, soonest due date first, current task + assignee visible without opening anything — the view built for the daily production meeting.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>WIP Meeting</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Manager, Job Coordinator</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>F007</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Production forecast, due-date-change reasons over time (push vs. pull), and idle-time (gap) reporting.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>F008</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Employees directory</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Staff list feeding every assignment dropdown in the tool.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Employees</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Admin, Manager</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Manager (+ Admin permission)</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>F009</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>In-app Getting Started guide</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>First thing a new tester sees — explains the tool, the stage lifecycle, who's meant to look at what, and how to import.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Guide / Onboarding</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Everyone</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>F010</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>BC import (.xlsx / CSV)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Upload a real Business Central "Job WIP Worksheet" export (or paste CSV/cells), map columns, upsert jobs by job number. Safe to re-run — a job already in progress never gets rewound.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>BC Import</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Job Coordinator</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>F011</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>In-browser .xlsx parser</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Hand-rolled ZIP + XML reader with zero external libraries (browser-native DEFLATE decompression). Fixed to read BC's real export correctly — its worksheet XML uses a namespace-prefixed root that a naive parser silently fails on.</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>BC Import</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="J15" s="10" t="n"/>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Root-caused against a real scrubbed BC export file, not a synthetic one.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>F012</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Delegation (live coverage)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>A team leader going on leave hands coverage to someone else (themself, another leader, or an employee stepping up). That person's actual open tasks, actions and owned jobs appear live on the delegate's dashboard, tagged "Covering for…", and disappear the moment the delegation ends — nothing manually reassigned.</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Delegation</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Team Leader / Production Owner, Manager</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Ashley</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="J16" s="10" t="n"/>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Reworked mid-build — first version only granted extra authority without moving the actual work; corrected per feedback.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>F013</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>BC import task-line triage</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>BC's task lines are generic, not job-specific, so an import queues candidate task lines instead of creating them directly. A job sits in a "Needs triage" panel until the coordinator/production owner selects what applies; rejected candidates are remembered so a re-import never brings them back.</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>BC Import</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Job Coordinator, Team Leader / Production Owner</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Ashley</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>F014</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Removed native browser dialogs</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Replaced every alert()/confirm() with in-page state-driven UI. Root cause of a real reported bug — the artifact's sandboxed iframe silently no-ops native dialogs, which made import look like it was doing nothing.</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Bug Fix</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Ashley</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>Confirmed via Playwright by reproducing the exact sandboxed-iframe behavior.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>F015</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Modal scroll-position fix</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Fixed a bug where any click that re-renders while a modal is open (e.g. editing a task's expected date) reset the modal's scroll to the top. Fixed centrally so it covers every modal interaction, not just the one reported button.</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Bug Fix</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Ashley</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>F016</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Job hold tracking</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Flag a job on hold with a category (Material, Client Info, Engineering, etc.) and a free-text reason, visible on the board.</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Job Board</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Job Coordinator</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>F017</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>All Actions / Register table</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>One filterable, sortable table of literally everything — production and non-production — for anyone who wants the flat view instead of the board.</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Action Register</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Everyone</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Built prior to this plan — see demo/wip-tracker-demo.html</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>F018</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Per-browser local persistence</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>State is saved to localStorage so a tester's data survives closing/reopening the tab. No server, no database yet — each tester's data is private to their own browser.</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>By design for this prototype phase — see "Reconcile data model" below for what replaces it.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>F019</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Real backend scaffold (separate track)</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Express + Prisma + React/Vite implementation exists in server/ and client/ with its own data model (User, Job, Task, DueDateChangeLog, TaskEvent, IdleGap) and API — built before the demo prototype, not yet reconciled with it.</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Initial build</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>See server/README.md and demo/README.md — the two data models diverge on purpose and need a deliberate reconciliation pass, not an assumption either one just wins.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>F020</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Reconcile demo vs. production data model</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Decide, feature by feature, which parts of the demo prototype's data model (action register, full stage lifecycle, delegation, triage) get built into the real server/Prisma schema, and rebuild the frontend against the real API.</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>Prerequisite for moving off the per-browser demo onto something shared/real.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>F021</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Real sign-in (SSO)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Replace the dev "type a known email" login with the company's actual identity provider before the tool holds any real client/job data.</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Likely SharePoint/Entra ID SSO, per the planned SharePoint hosting.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>F022</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Host on SharePoint</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Stand up the real (non-demo) tool on SharePoint so the team works from one shared copy instead of individual browser sandboxes.</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="10" t="n"/>
+      <c r="K26" s="10" t="n"/>
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>Mentioned as the near-term plan — work is expected to move to GitHub-based development ahead of this.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="44" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>F023</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>A daily digest (email/Teams) of what's overdue or handing over today, so the dashboard isn't the only place this surfaces.</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Everyone</t>
         </is>
       </c>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="10" t="n"/>
+      <c r="K27" s="10" t="n"/>
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>Carried over from server/README.md suggested next features.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>F024</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>BC write-back</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Once a job's tasks are all complete, optionally post a status/% back to Business Central so the two systems don't diverge.</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>BC Import</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="10" t="n"/>
+      <c r="K28" s="10" t="n"/>
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>Carried over from server/README.md suggested next features.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="44" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>F025</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Mobile-friendly My Dashboard</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>A mobile-friendly view of "My Actions" specifically — the screen staff will open most, often not at a desk.</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Enhancement</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>My Dashboard</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Workshop / Trade Staff</t>
         </is>
       </c>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>Carried over from server/README.md suggested next features.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="44" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>F026</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Capacity view</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Alongside open-task counts, a rough hours-remaining estimate per person — task count alone doesn't distinguish a 20-minute task from a two-week one.</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Team / Manager View</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>P3 - Low</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Team Leader / Production Owner, Manager</t>
         </is>
       </c>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>Carried over from server/README.md suggested next features.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="44" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>F027</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Comments/mentions on a task</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>A quick note on a task (e.g. "waiting on you to check X") for the handful of times that's genuinely useful — kept optional so it doesn't become another data-entry chore.</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>My Dashboard</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>P3 - Low</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Everyone</t>
         </is>
       </c>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>Carried over from server/README.md suggested next features.</t>
         </is>
       </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>F028</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Job lifetime tracking</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>We need to implement both a visual and numerical breakdown of the path a job took and the time spent at each stage and sitting idle at each stage</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>P2 - Medium</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Team leaders, supervisors, management</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>F029</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Employee definition/org chart</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Set the employees view up more like an org chart. We want defined roles to choose from rather than just typing in a role. Specific roles will have visibility of specific things; the end goal here being that people in any given role will see everything they need to see, and nothing they don't. Adding responsibility to a role needs to be a deliberate decision, rather than just a case of "scope creep"</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>P2 - Medium</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K33" s="10" t="n"/>
+      <c r="L33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>F030</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Admin authority</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>An admin permission level needs to be established, as people with this permission level will be the ones adding and modifying roles, arranging the org chart, etc</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>P0 - Critical</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K34" s="10" t="n"/>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Modeled on the Roles sheet as a Permission Level, not a role — flagged by Ashley: nobody's whole job here is running this tool, so Admin is a capability applied to whichever role(s) need it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>F031</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Job deletion for testing</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>For testing purposes, we need to implement a quick way to delete bulk jobs. For example, I did an import before the previous change to introduce the triage stage, so now I have of 100 jobs on the board that haven't been triaged so I want to delete them all and do the import again</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Idea</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F31">
+  <conditionalFormatting sqref="F5:F35">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -2803,7 +3100,7 @@
       <formula>"Won't Do"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G31">
+  <conditionalFormatting sqref="G5:G35">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
       <formula>"P0 - Critical"</formula>
     </cfRule>
@@ -2863,164 +3160,164 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Counts pull live from Features &amp; Backlog — nothing to update by hand.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>By Status</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>By Priority</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="C6" s="9">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$31,B6)</f>
+      <c r="C6" s="12">
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B6)</f>
         <v/>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="F6" s="9">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$31,E6)</f>
+      <c r="F6" s="12">
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$35,E6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="C7" s="9">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$31,B7)</f>
+      <c r="C7" s="12">
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B7)</f>
         <v/>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="F7" s="9">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$31,E7)</f>
+      <c r="F7" s="12">
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$35,E7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="C8" s="9">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$31,B8)</f>
+      <c r="C8" s="12">
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B8)</f>
         <v/>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="F8" s="9">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$31,E8)</f>
+      <c r="F8" s="12">
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$35,E8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="C9" s="9">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$31,B9)</f>
+      <c r="C9" s="12">
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B9)</f>
         <v/>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>P3 - Low</t>
         </is>
       </c>
-      <c r="F9" s="9">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$31,E9)</f>
+      <c r="F9" s="12">
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$35,E9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="C10" s="9">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$31,B10)</f>
+      <c r="C10" s="12">
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B10)</f>
         <v/>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="13">
         <f>SUM(F6:F9)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Won't Do</t>
         </is>
       </c>
-      <c r="C11" s="9">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$31,B11)</f>
+      <c r="C11" s="12">
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="13">
         <f>SUM(C6:C11)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Not yet started (Idea + Backlog + Planned)</t>
         </is>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="12">
         <f>C6+C7+C8</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>% complete (Done ÷ Total)</t>
         </is>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="14">
         <f>C10/C12</f>
         <v/>
       </c>

--- a/planning/WIP_Tracker_App_Development_Plan.xlsx
+++ b/planning/WIP_Tracker_App_Development_Plan.xlsx
@@ -2904,7 +2904,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2925,8 +2925,14 @@
       <c r="J32" s="10" t="n">
         <v>46262</v>
       </c>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="5" t="n"/>
+      <c r="K32" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Collapsible "Job lifetime" panel in the job modal: proportional stage timeline + per-stage day counts, plus a separate on-hold/idle log (start/end, category, reason). Tracking starts from when this shipped — history before that isn't reconstructed for jobs already in flight.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -2956,7 +2962,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -2973,8 +2979,14 @@
       <c r="J33" s="10" t="n">
         <v>46262</v>
       </c>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="5" t="n"/>
+      <c r="K33" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Employees now has a List/Org chart toggle (tree by manager) and a defined Role dropdown (from the Roles sheet's draft list) alongside free-text Job Title. The dropdown is descriptive only for now — it doesn't yet gate what a role can see elsewhere in the app, since the taxonomy isn't finalized. Wiring real per-role visibility off this field is a good next backlog item once Roles firms up.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -3004,7 +3016,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -3021,10 +3033,12 @@
       <c r="J34" s="10" t="n">
         <v>46262</v>
       </c>
-      <c r="K34" s="10" t="n"/>
+      <c r="K34" s="10" t="n">
+        <v>46262</v>
+      </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Modeled on the Roles sheet as a Permission Level, not a role — flagged by Ashley: nobody's whole job here is running this tool, so Admin is a capability applied to whichever role(s) need it.</t>
+          <t>Modeled on the Roles sheet as a Permission Level, not a role — flagged by Ashley: nobody's whole job here is running this tool, so Admin is a capability applied to whichever role(s) need it. Shipped as an isAdmin checkbox per employee; only Admins can add/edit employees, reassign managers, or grant Admin. A guard blocks removing the last Admin. Priya holds it by default in the sample data.</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3070,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -3073,8 +3087,14 @@
       <c r="J35" s="10" t="n">
         <v>46262</v>
       </c>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="5" t="n"/>
+      <c r="K35" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Admin-only "☑ Select jobs" mode on the Job Board — checkboxes on every card and Needs Triage row, a one-click "Select all in Needs triage", and a confirmed bulk delete that cascades to that job's task lines.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/planning/WIP_Tracker_App_Development_Plan.xlsx
+++ b/planning/WIP_Tracker_App_Development_Plan.xlsx
@@ -385,8 +385,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L35" headerRowCount="1">
-  <autoFilter ref="A4:L35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L36" headerRowCount="1">
+  <autoFilter ref="A4:L36"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Feature / Idea"/>
@@ -1393,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3096,11 +3096,65 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>F032</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Needs Triage panel visual fix</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>The 'needs triage' view needs a UI change. When there's a list of jobs there it's just a big patch of yellow and looks awful</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Job Board</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>P2 - Medium</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K36" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Panel was a full warn-soft fill with individually-carded rows — the gaps between cards read as a solid yellow block once more than one or two jobs were queued. Switched to the same clean pattern as Pending Approvals: white panel with a thin amber border, rows divided by hairlines instead of separate cards, and small amber badges (count + "Review") instead of a painted background.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F35">
+  <conditionalFormatting sqref="F5:F36">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -3120,7 +3174,7 @@
       <formula>"Won't Do"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G35">
+  <conditionalFormatting sqref="G5:G36">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
       <formula>"P0 - Critical"</formula>
     </cfRule>
@@ -3205,7 +3259,7 @@
         </is>
       </c>
       <c r="C6" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B6)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B6)</f>
         <v/>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -3214,7 +3268,7 @@
         </is>
       </c>
       <c r="F6" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$35,E6)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$36,E6)</f>
         <v/>
       </c>
     </row>
@@ -3225,7 +3279,7 @@
         </is>
       </c>
       <c r="C7" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B7)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B7)</f>
         <v/>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -3234,7 +3288,7 @@
         </is>
       </c>
       <c r="F7" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$35,E7)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$36,E7)</f>
         <v/>
       </c>
     </row>
@@ -3245,7 +3299,7 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B8)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B8)</f>
         <v/>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -3254,7 +3308,7 @@
         </is>
       </c>
       <c r="F8" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$35,E8)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$36,E8)</f>
         <v/>
       </c>
     </row>
@@ -3265,7 +3319,7 @@
         </is>
       </c>
       <c r="C9" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B9)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B9)</f>
         <v/>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -3274,7 +3328,7 @@
         </is>
       </c>
       <c r="F9" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$35,E9)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$36,E9)</f>
         <v/>
       </c>
     </row>
@@ -3285,7 +3339,7 @@
         </is>
       </c>
       <c r="C10" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B10)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B10)</f>
         <v/>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -3305,7 +3359,7 @@
         </is>
       </c>
       <c r="C11" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$35,B11)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B11)</f>
         <v/>
       </c>
     </row>

--- a/planning/WIP_Tracker_App_Development_Plan.xlsx
+++ b/planning/WIP_Tracker_App_Development_Plan.xlsx
@@ -385,8 +385,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L36" headerRowCount="1">
-  <autoFilter ref="A4:L36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L39" headerRowCount="1">
+  <autoFilter ref="A4:L39"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Feature / Idea"/>
@@ -1393,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3150,11 +3150,173 @@
         </is>
       </c>
     </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>F033</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Add/re-organise task lines</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>The triage stage requires functionality for adding and re-organising task lines. The ability to hover the mouse cursor between two task lines and have a + appear on the right hand side to click and add a line would be the most efficient way, rather than having new tasks added at the top or bottom and needing to be repositioned. Re-organising of</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Job Board</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>A hover-revealed "+" divider sits between every task line (and before the first / after the last) on a Production job — click to open the add-task form right there, inserting at that exact position instead of always appending. Re-ordering is drag-and-drop via a ⠿ handle on each line. (Note: this was renumbered from the F032 you assigned it — that ID landed on a fix already in flight when your file was created; nothing about the request itself changed.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>F034</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Tree-style org chart</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>A tree-style org chart would look better and be clearer than the current list-style. The ability to drag-and-drop staff around to organise the chart would also be beneficial</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>P2 - Medium</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K38" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Rebuilt as a real branching tree with connector lines (CSS, not an image/library), scrolling horizontally for wide trees. Admins can drag one card onto another to reassign who they report to; a guard blocks dropping someone onto their own report (would create a management loop). Renumbered from your F033 for the same ID-collision reason as F033 above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="44" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>F035</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Analytics view bug</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>The analytics view doesn't seem to be visible to anyone</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K39" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Root cause wasn't Analytics itself (its nav gate is unconditional) — the sidebar is a fixed-height column with no scroll, so on a shorter window (or a constrained viewer like the Artifact frame) its 8 nav items + viewer picker + footer overflow the bottom with no way to reach the items past the fold. Analytics and Employees, being lowest in the list, were the ones most likely to disappear. Fixed by making the sidebar scrollable when its content doesn't fit. Renumbered from your F034 for the same ID-collision reason as F033/F034 above.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F36">
+  <conditionalFormatting sqref="F5:F39">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -3174,7 +3336,7 @@
       <formula>"Won't Do"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G36">
+  <conditionalFormatting sqref="G5:G39">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
       <formula>"P0 - Critical"</formula>
     </cfRule>
@@ -3259,7 +3421,7 @@
         </is>
       </c>
       <c r="C6" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B6)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B6)</f>
         <v/>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -3268,7 +3430,7 @@
         </is>
       </c>
       <c r="F6" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$36,E6)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$39,E6)</f>
         <v/>
       </c>
     </row>
@@ -3279,7 +3441,7 @@
         </is>
       </c>
       <c r="C7" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B7)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B7)</f>
         <v/>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -3288,7 +3450,7 @@
         </is>
       </c>
       <c r="F7" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$36,E7)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$39,E7)</f>
         <v/>
       </c>
     </row>
@@ -3299,7 +3461,7 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B8)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B8)</f>
         <v/>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -3308,7 +3470,7 @@
         </is>
       </c>
       <c r="F8" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$36,E8)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$39,E8)</f>
         <v/>
       </c>
     </row>
@@ -3319,7 +3481,7 @@
         </is>
       </c>
       <c r="C9" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B9)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B9)</f>
         <v/>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -3328,7 +3490,7 @@
         </is>
       </c>
       <c r="F9" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$36,E9)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$39,E9)</f>
         <v/>
       </c>
     </row>
@@ -3339,7 +3501,7 @@
         </is>
       </c>
       <c r="C10" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B10)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B10)</f>
         <v/>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -3359,7 +3521,7 @@
         </is>
       </c>
       <c r="C11" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$36,B11)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B11)</f>
         <v/>
       </c>
     </row>

--- a/planning/WIP_Tracker_App_Development_Plan.xlsx
+++ b/planning/WIP_Tracker_App_Development_Plan.xlsx
@@ -3200,7 +3200,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>A hover-revealed "+" divider sits between every task line (and before the first / after the last) on a Production job — click to open the add-task form right there, inserting at that exact position instead of always appending. Re-ordering is drag-and-drop via a ⠿ handle on each line. (Note: this was renumbered from the F032 you assigned it — that ID landed on a fix already in flight when your file was created; nothing about the request itself changed.)</t>
+          <t>A hover-revealed "+" divider sits between every task line (and before the first / after the last), click to open the add-task form right there, inserting at that exact position instead of always appending. Re-ordering is drag-and-drop via a ⠿ handle on each line. First pass wrongly gated this to the Production stage only — since triage can hand a job real task lines while it's still at Order Received, that hid the whole feature on exactly the jobs it was built for. Fixed to work at any stage. (Renumbered from the F032 you assigned it — that ID landed on a fix already in flight when your file was created; nothing about the request itself changed.)</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Root cause wasn't Analytics itself (its nav gate is unconditional) — the sidebar is a fixed-height column with no scroll, so on a shorter window (or a constrained viewer like the Artifact frame) its 8 nav items + viewer picker + footer overflow the bottom with no way to reach the items past the fold. Analytics and Employees, being lowest in the list, were the ones most likely to disappear. Fixed by making the sidebar scrollable when its content doesn't fit. Renumbered from your F034 for the same ID-collision reason as F033/F034 above.</t>
+          <t>First pass misdiagnosed this as the sidebar overflowing on a short window (fixed that too, harmless either way, but it wasn't the real cause). Actual root cause: bulk-deleting a job (F031) removed its tasks but left that job's due-date-change and idle-gap history dangling, referencing a job/task that no longer existed; Analytics rendered that history unguarded and threw, which silently aborted the render mid-way and left whatever view was already on screen showing — exactly "clicking does nothing." Fixed at the source (delete now cascades fully, and a one-time pass on load cleans up anyone's browser already carrying orphaned history from before this fix), guarded defensively in Analytics itself, and wrapped every view's render in error isolation so a future bug like this surfaces a visible error instead of silently freezing the screen. Renumbered from your F034 for the same ID-collision reason as F033/F034 above.</t>
         </is>
       </c>
     </row>

--- a/planning/WIP_Tracker_App_Development_Plan.xlsx
+++ b/planning/WIP_Tracker_App_Development_Plan.xlsx
@@ -3200,7 +3200,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>A hover-revealed "+" divider sits between every task line (and before the first / after the last), click to open the add-task form right there, inserting at that exact position instead of always appending. Re-ordering is drag-and-drop via a ⠿ handle on each line. First pass wrongly gated this to the Production stage only — since triage can hand a job real task lines while it's still at Order Received, that hid the whole feature on exactly the jobs it was built for. Fixed to work at any stage. (Renumbered from the F032 you assigned it — that ID landed on a fix already in flight when your file was created; nothing about the request itself changed.)</t>
+          <t>Live in two places now, both with the same hover-"+"-divider / drag-⠿-to-reorder mechanic: (1) the job-board task-line list, at any stage (first pass wrongly limited this to Production, which hid it on jobs fresh out of triage — fixed); (2) the triage modal itself, per the original ask — a coordinator can add a candidate BC never sent and reorder the candidate list, and that order is exactly the order the real task lines land in once confirmed. (Renumbered from the F032 you assigned it — that ID landed on a fix already in flight when your file was created; nothing about the request itself changed.)</t>
         </is>
       </c>
     </row>

--- a/planning/WIP_Tracker_App_Development_Plan.xlsx
+++ b/planning/WIP_Tracker_App_Development_Plan.xlsx
@@ -385,8 +385,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L39" headerRowCount="1">
-  <autoFilter ref="A4:L39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L41" headerRowCount="1">
+  <autoFilter ref="A4:L41"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Feature / Idea"/>
@@ -1393,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3312,11 +3312,119 @@
         </is>
       </c>
     </row>
+    <row r="40" ht="44" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>F036</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Triage: remove instead of uncheck</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Rather than checking or unchecking lines, let's just have an X to remove unwanted steps and have them disappear entirely. Trying to re-order wanted task lines around unchecked and therefore unwanted task lines is a clunky way to do things.</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>BC Import</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Checkbox model removed from the triage modal entirely — every candidate shown is, by definition, one that'll become a task line; a ✕ per row removes it from the list outright (still remembered as rejected, same as an unchecked one used to be, so it doesn't resurface on a re-import). Confirm now just adds whatever's left. Found and fixed a real data-loss bug while building the paired template feature below: renaming a template and then immediately typing into another field on the same modal could silently drop the second field's text, because the rename's change handler triggered a full re-render on blur, mid-keystroke, wiping the freshly-focused input before its value ever reached state — fixed by having the rename update state without forcing a render.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="44" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>F037</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Task line templates</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Let's also implement templates - pre-defined sets of task lines that can be selected at the triage stage that would completely replace any lines that were brought in during import</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>BC Import</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>A template picker on the triage modal applies a named, pre-defined task-line set — with confirmation, since it completely replaces whatever's currently queued (from BC, hand-typed, or a prior template), not merged with it; discarded candidates are remembered as rejected the same as an explicit ✕. Templates themselves are company-wide, persisted, and managed via an Admin-gated "⚙ Manage templates" modal (add/rename/delete a template; add/remove/drag-reorder its task lines) — everyone else gets a read-only view. Seeded 3 example templates (HVOF/Plasma Coating, Structural Fabrication, Weld Repair) matching the demo's existing task-line vocabulary.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F39">
+  <conditionalFormatting sqref="F5:F41">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -3336,7 +3444,7 @@
       <formula>"Won't Do"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G39">
+  <conditionalFormatting sqref="G5:G41">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
       <formula>"P0 - Critical"</formula>
     </cfRule>
@@ -3421,7 +3529,7 @@
         </is>
       </c>
       <c r="C6" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B6)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B6)</f>
         <v/>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -3430,7 +3538,7 @@
         </is>
       </c>
       <c r="F6" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$39,E6)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$41,E6)</f>
         <v/>
       </c>
     </row>
@@ -3441,7 +3549,7 @@
         </is>
       </c>
       <c r="C7" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B7)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B7)</f>
         <v/>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -3450,7 +3558,7 @@
         </is>
       </c>
       <c r="F7" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$39,E7)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$41,E7)</f>
         <v/>
       </c>
     </row>
@@ -3461,7 +3569,7 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B8)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B8)</f>
         <v/>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -3470,7 +3578,7 @@
         </is>
       </c>
       <c r="F8" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$39,E8)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$41,E8)</f>
         <v/>
       </c>
     </row>
@@ -3481,7 +3589,7 @@
         </is>
       </c>
       <c r="C9" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B9)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B9)</f>
         <v/>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -3490,7 +3598,7 @@
         </is>
       </c>
       <c r="F9" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$39,E9)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$41,E9)</f>
         <v/>
       </c>
     </row>
@@ -3501,7 +3609,7 @@
         </is>
       </c>
       <c r="C10" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B10)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B10)</f>
         <v/>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -3521,7 +3629,7 @@
         </is>
       </c>
       <c r="C11" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$39,B11)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B11)</f>
         <v/>
       </c>
     </row>

--- a/planning/WIP_Tracker_App_Development_Plan.xlsx
+++ b/planning/WIP_Tracker_App_Development_Plan.xlsx
@@ -385,8 +385,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L41" headerRowCount="1">
-  <autoFilter ref="A4:L41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L42" headerRowCount="1">
+  <autoFilter ref="A4:L42"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Feature / Idea"/>
@@ -1393,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3416,7 +3416,61 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>A template picker on the triage modal applies a named, pre-defined task-line set — with confirmation, since it completely replaces whatever's currently queued (from BC, hand-typed, or a prior template), not merged with it; discarded candidates are remembered as rejected the same as an explicit ✕. Templates themselves are company-wide, persisted, and managed via an Admin-gated "⚙ Manage templates" modal (add/rename/delete a template; add/remove/drag-reorder its task lines) — everyone else gets a read-only view. Seeded 3 example templates (HVOF/Plasma Coating, Structural Fabrication, Weld Repair) matching the demo's existing task-line vocabulary.</t>
+          <t>A template picker on the triage modal applies a named, pre-defined task-line set — with confirmation, since it completely replaces whatever's currently queued (from BC, hand-typed, or a prior template), not merged with it; discarded candidates are remembered as rejected the same as an explicit ✕. Templates themselves are company-wide, persisted, and managed (add/rename/delete a template; add/remove/drag-reorder its task lines) on an Admin-gated page — see F038, moved off its original modal. Seeded 3 example templates (HVOF/Plasma Coating, Structural Fabrication, Weld Repair) matching the demo's existing task-line vocabulary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>F038</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Nav submenus + Templates as its own page</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Rather than having the 'manage templates' being a list of templates in a modal - which will get cumbersome very quickly - let's make it its own page. A sub-menu option nested under job board in the nav bar. If we don't already have sub-menu functionality planned in, then we'll do that now for all the options in the nav bar as most of them will likely get sub-menu options later down the track</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K42" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Built generic submenu support into the sidebar nav rather than a one-off for Templates: any NAV_ITEMS entry can carry an optional children array and the rendering/click-handling is written against that generically, so adding a submenu to Team, Analytics, etc. later needs no new plumbing — just add children. A parent with children shows a chevron (its own click target, toggles independently of navigating); the submenu auto-expands whenever one of its children is the active page, so a direct link into a sub-page never leaves the group looking collapsed. Task Line Templates is the first submenu item, nested under Job Board, and moved off its modal onto its own page — a modal was going to get cramped as the template list grew, per your note.</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3478,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F41">
+  <conditionalFormatting sqref="F5:F42">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -3444,7 +3498,7 @@
       <formula>"Won't Do"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G41">
+  <conditionalFormatting sqref="G5:G42">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
       <formula>"P0 - Critical"</formula>
     </cfRule>
@@ -3529,7 +3583,7 @@
         </is>
       </c>
       <c r="C6" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B6)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B6)</f>
         <v/>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -3538,7 +3592,7 @@
         </is>
       </c>
       <c r="F6" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$41,E6)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$42,E6)</f>
         <v/>
       </c>
     </row>
@@ -3549,7 +3603,7 @@
         </is>
       </c>
       <c r="C7" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B7)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B7)</f>
         <v/>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -3558,7 +3612,7 @@
         </is>
       </c>
       <c r="F7" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$41,E7)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$42,E7)</f>
         <v/>
       </c>
     </row>
@@ -3569,7 +3623,7 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B8)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B8)</f>
         <v/>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -3578,7 +3632,7 @@
         </is>
       </c>
       <c r="F8" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$41,E8)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$42,E8)</f>
         <v/>
       </c>
     </row>
@@ -3589,7 +3643,7 @@
         </is>
       </c>
       <c r="C9" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B9)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B9)</f>
         <v/>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -3598,7 +3652,7 @@
         </is>
       </c>
       <c r="F9" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$41,E9)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$42,E9)</f>
         <v/>
       </c>
     </row>
@@ -3609,7 +3663,7 @@
         </is>
       </c>
       <c r="C10" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B10)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B10)</f>
         <v/>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -3629,7 +3683,7 @@
         </is>
       </c>
       <c r="C11" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$41,B11)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B11)</f>
         <v/>
       </c>
     </row>

--- a/planning/WIP_Tracker_App_Development_Plan.xlsx
+++ b/planning/WIP_Tracker_App_Development_Plan.xlsx
@@ -385,8 +385,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L42" headerRowCount="1">
-  <autoFilter ref="A4:L42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FeaturesTable" displayName="FeaturesTable" ref="A4:L46" headerRowCount="1">
+  <autoFilter ref="A4:L46"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Feature / Idea"/>
@@ -1393,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3474,11 +3474,235 @@
         </is>
       </c>
     </row>
+    <row r="43" ht="44" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>F039</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Editable lines in task templates</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Once lines are added to a task line template they are not individually editable, the only option is to delete it and add a new one, then re-organise it into place. This is a waste of time so we need the ability to directly edit each task line.</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Job Board</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>P2 - Medium</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Each task line on the Templates page is now a text input, not a static label — edit it in place and it saves on blur/change, no more delete-and-re-add-then-reorder round trip. Applied the same no-render-on-change fix used for template renaming (F036) so typing here and then clicking into another line can't silently drop a keystroke. The row itself is no longer statically draggable (that conflicted with selecting text inside the new input) — dragging is now only armed when the mousedown starts on the ⠿ handle, so drag-to-reorder still works exactly as before alongside the new editing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>F040</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Supervisor/manager dashboard view changes</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Anyone with employees reporting to them should have visibility over their actions that require attention. For example, if a supervisor has a team leader below them with an at risk or overdue task, that should be flagged on the supervisors dashboard.</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>My Dashboard</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Team rollup counts (open/overdue/due soon/done) now sum a direct report's entire reporting chain, not just their own items — so a skip-level manager sees a team leader's own team's overdue work reflected against that team leader's row on Team, which is exactly what wasn't visible before. Also added a "Team Needs Attention" panel to My Dashboard itself for any manager, listing every direct report with an overdue or at-risk item anywhere in their subtree, sorted worst-first, each row clicking straight through to that person's expanded row on Team. The existing Team nav badge picks up the same deeper counts automatically since it was already built on this rollup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="44" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>F041</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Delegation view improvements</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Delegations that have ended should disappear from view and the delegations section should be below the actual team listing, otherwise the team view would just be a list of old delegations with a the actual useful info at the bottom of the page.</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Team / Manager View</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>P2 - Medium</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>Delegated coverage panel now renders below the team listing on the Team page instead of above it, and the table only ever lists currently-active delegations — one that's ended drops off the list entirely the moment its end date passes, rather than sticking around tagged "Ended." The "End now" action is unaffected for the delegations still showing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="44" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>F042</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Welder/boilermaker pool usage</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>There is currently no way for the team leaders to assign task lines to the previously defined pools of employees, this needs to be implemented.</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Job Board</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Team Leader / Production Owner</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Pool assignment already existed when a task line was first created, but the Reassign control on an already-existing line only ever offered picking a different person, and was hidden entirely once a line was pool-assigned — meaning a pool-assigned task could never be touched again, and since real task lines mostly come out of triage (always created unassigned to an individual), pool assignment was in practice unreachable for the bulk of task lines. Reassign is now a 3-way switch — person / Welding Workshop pool (with a headcount field) / vendor — available on any task line at any time, in either direction, not just at creation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F42">
+  <conditionalFormatting sqref="F5:F46">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -3498,7 +3722,7 @@
       <formula>"Won't Do"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G42">
+  <conditionalFormatting sqref="G5:G46">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
       <formula>"P0 - Critical"</formula>
     </cfRule>
@@ -3583,7 +3807,7 @@
         </is>
       </c>
       <c r="C6" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B6)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$46,B6)</f>
         <v/>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -3592,7 +3816,7 @@
         </is>
       </c>
       <c r="F6" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$42,E6)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$46,E6)</f>
         <v/>
       </c>
     </row>
@@ -3603,7 +3827,7 @@
         </is>
       </c>
       <c r="C7" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B7)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$46,B7)</f>
         <v/>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -3612,7 +3836,7 @@
         </is>
       </c>
       <c r="F7" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$42,E7)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$46,E7)</f>
         <v/>
       </c>
     </row>
@@ -3623,7 +3847,7 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B8)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$46,B8)</f>
         <v/>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -3632,7 +3856,7 @@
         </is>
       </c>
       <c r="F8" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$42,E8)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$46,E8)</f>
         <v/>
       </c>
     </row>
@@ -3643,7 +3867,7 @@
         </is>
       </c>
       <c r="C9" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B9)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$46,B9)</f>
         <v/>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -3652,7 +3876,7 @@
         </is>
       </c>
       <c r="F9" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$42,E9)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$G$5:$G$46,E9)</f>
         <v/>
       </c>
     </row>
@@ -3663,7 +3887,7 @@
         </is>
       </c>
       <c r="C10" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B10)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$46,B10)</f>
         <v/>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -3683,7 +3907,7 @@
         </is>
       </c>
       <c r="C11" s="12">
-        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$42,B11)</f>
+        <f>COUNTIF('Features &amp; Backlog'!$F$5:$F$46,B11)</f>
         <v/>
       </c>
     </row>
